--- a/public/examples/example_trial_balance_6col.xlsx
+++ b/public/examples/example_trial_balance_6col.xlsx
@@ -456,7 +456,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CUI RO 90000001   Nr. Reg. Com. J99/9999/2099   CAEN 1039</t>
+          <t>CUI RO 99999999   Nr. Reg. Com. J99/9999/2099   CAEN 1039</t>
         </is>
       </c>
     </row>

--- a/public/examples/example_trial_balance_6col.xlsx
+++ b/public/examples/example_trial_balance_6col.xlsx
@@ -480,7 +480,7 @@
       <c r="B6" s="1" t="n"/>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Solduri initiale an</t>
+          <t>Solduri inițiale an</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
